--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02ECB78F-B91A-45E1-A8A8-BAE0B3AE54D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDDE4026-BAA8-4480-9398-E50050783458}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{635BFE64-A287-4BA6-9595-2A728AB900AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15025E90-FE52-41B1-A78F-2E7CC05C5095}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99A28D2E-E2CF-4F6D-A42D-C0E197CF9B18}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D807F45-220E-4B03-BAB5-A3529E10EDF5}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDDE4026-BAA8-4480-9398-E50050783458}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6DDCE34-9FC4-489E-9699-C87095293AE9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15025E90-FE52-41B1-A78F-2E7CC05C5095}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDE556E-306A-4CC6-B911-1BAFE1E252F2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D807F45-220E-4B03-BAB5-A3529E10EDF5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCC6746D-65E4-4F97-9D53-24211E13B7E3}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6DDCE34-9FC4-489E-9699-C87095293AE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1193AB3D-89CF-4D04-9D6B-19BA3A11AC58}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDE556E-306A-4CC6-B911-1BAFE1E252F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D46BE40-4792-4638-ABEF-1B8209127580}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCC6746D-65E4-4F97-9D53-24211E13B7E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{406AEC2C-0157-410E-AE77-67DBC2862FF0}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1844,13 +1844,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1193AB3D-89CF-4D04-9D6B-19BA3A11AC58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0D7F67E-7D08-4BE0-A898-C0A5811FC1B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D46BE40-4792-4638-ABEF-1B8209127580}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82ED1F59-D954-4FB9-8598-6CFE01C8DC04}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{406AEC2C-0157-410E-AE77-67DBC2862FF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F885A6AD-2CE8-41E9-9298-F030E82C04FF}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -11,6 +11,204 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="64">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>vocal_repertoire_size_MS2005</t>
+  </si>
+  <si>
+    <t>vocal_repertoire_size_MS2005_Source</t>
+  </si>
+  <si>
+    <t>vocal_repertoire_size_updated</t>
+  </si>
+  <si>
+    <t>vocal_repertoire_size_updated_Source</t>
+  </si>
+  <si>
+    <t>Alouatta palliata</t>
+  </si>
+  <si>
+    <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
+  </si>
+  <si>
+    <t>Arctocebus calabarensis</t>
+  </si>
+  <si>
+    <t>Callicebus moloch</t>
+  </si>
+  <si>
+    <t>Muir, J., Ravuri, A., Meissner, E., Hawes, J. E., Dufourq, E., O’Mahoney, T., &amp; Dunn, J. C. (2025). Detection and classification of captive coppery titi monkey calls. Bioacoustics, 34(4), 400–418. https://doi.org/10.1080/09524622.2025.2496497</t>
+  </si>
+  <si>
+    <t>Callimico goeldii</t>
+  </si>
+  <si>
+    <t>Callithrix jacchus</t>
+  </si>
+  <si>
+    <t>Bosshard, A. B., Burkart, J. M., Merlo, P., Cathcart, C., Townsend, S. W., &amp; Bickel, B. (2024). Beyond bigrams: Call sequencing in the common marmoset (Callithrix jacchus) vocal system. Royal Society Open Science, 11(11), 240218. https://doi.org/10.1098/rsos.240218</t>
+  </si>
+  <si>
+    <t>Callithrix pygmaea</t>
+  </si>
+  <si>
+    <t>Cebuella pygmaea</t>
+  </si>
+  <si>
+    <t>Cebus olivaceus</t>
+  </si>
+  <si>
+    <t>Cercocebus torquatus</t>
+  </si>
+  <si>
+    <t>Bouchet, H., Pellier, A.-S., Blois-Heulin, C., &amp; Lemasson, A. (2010). Sex differences in the vocal repertoire of adult red-capped mangabeys (Cercocebus torquatus): A multi-level acoustic analysis. American Journal of Primatology, 72(4), 360–375. https://doi.org/10.1002/ajp.20791</t>
+  </si>
+  <si>
+    <t>Cercopithecus cephus</t>
+  </si>
+  <si>
+    <t>Chlorocebus aethiops</t>
+  </si>
+  <si>
+    <t>Daubentonia madagascariensis</t>
+  </si>
+  <si>
+    <t>Eulemur fulvus</t>
+  </si>
+  <si>
+    <t>Fichtel, C., &amp; Kappeler, P. M. (2022). Coevolution of social and communicative complexity in lemurs. Philosophical Transactions of the Royal Society B: Biological Sciences, 377(1860), 20210297. https://doi.org/10.1098/rstb.2021.0297
+Gamba, M., Friard, O., Riondato, I., Righini, R., Colombo, C., Miaretsoa, L., Torti, V., Nadhurou, B., &amp; Giacoma, C. (2015). Comparative Analysis of the Vocal Repertoire of Eulemur: A Dynamic Time Warping Approach. International Journal of Primatology, 36(5), 894–910. https://doi.org/10.1007/s10764-015-9861-1</t>
+  </si>
+  <si>
+    <t>Eulemur macaco</t>
+  </si>
+  <si>
+    <t>Fichtel, C., &amp; Kappeler, P. M. (2022). Coevolution of social and communicative complexity in lemurs. Philosophical Transactions of the Royal Society B: Biological Sciences, 377(1860), 20210297. https://doi.org/10.1098/rstb.2021.0297</t>
+  </si>
+  <si>
+    <t>Eulemur mongoz</t>
+  </si>
+  <si>
+    <t>Nadhurou, B., Gamba, M., Andriaholinirina, N. V., Ouledi, A., &amp; Giacoma, C. (2016). The vocal communication of the mongoose lemur (Eulemur mongoz): Phonation mechanisms, acoustic features and quantitative analysis. Ethology Ecology &amp; Evolution, 28(3), 241–260. https://doi.org/10.1080/03949370.2015.1039069</t>
+  </si>
+  <si>
+    <t>Euoticus elegantulus</t>
+  </si>
+  <si>
+    <t>Galago alleni</t>
+  </si>
+  <si>
+    <t>Galago senegalensis</t>
+  </si>
+  <si>
+    <t>Galagoides demidoff</t>
+  </si>
+  <si>
+    <t>Galago demidovii</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Salmi, R., Hammerschmidt, K., &amp; Doran-Sheehy, D. M. (2013). Western Gorilla Vocal Repertoire and Contextual Use of Vocalizations. Ethology, 119(10), 831–847. https://doi.org/10.1111/eth.12122</t>
+  </si>
+  <si>
+    <t>Lagothrix lagothricha</t>
+  </si>
+  <si>
+    <t>León, J. J., Vargas, S. A., Ramírez, M. A., Galvis, N. F., Cifuentes, E. F., &amp; Stevenson, P. R. (2014). Vocal Communication in Woolly Monkeys (Lagothrixlagothricha lugens) in Cueva de los Guacharos National Park, Colombia. In T. R. Defler &amp; P. R. Stevenson (Eds), The Woolly Monkey: Behavior, Ecology, Systematics, and Captive Research (pp. 187–205). Springer. https://doi.org/10.1007/978-1-4939-0697-0 11</t>
+  </si>
+  <si>
+    <t>Lemur catta</t>
+  </si>
+  <si>
+    <t>Leontopithecus rosalia</t>
+  </si>
+  <si>
+    <t>Lopes, R. J. (2020). Mission marmoset. Nature, 579(7799), 464. https://doi.org/10.1038/d41586-020-00770-6</t>
+  </si>
+  <si>
+    <t>Macaca fascicularis</t>
+  </si>
+  <si>
+    <t>Macaca fuscata</t>
+  </si>
+  <si>
+    <t>Macaca nemestrina</t>
+  </si>
+  <si>
+    <t>Macaca radiata</t>
+  </si>
+  <si>
+    <t>Macaca silenus</t>
+  </si>
+  <si>
+    <t>Macaca sylvanus</t>
+  </si>
+  <si>
+    <t>Mandrillus sphinx</t>
+  </si>
+  <si>
+    <t>Miopithecus talapoin</t>
+  </si>
+  <si>
+    <t>Pan paniscus</t>
+  </si>
+  <si>
+    <t>Wegdell, F., Schamberg, I., Berthet, M., Rothacher, Y., Dellwo, V., Surbeck, M., &amp; Townsend, S. W. (2025). An updated vocal repertoire of wild adult bonobos (Pan paniscus ) (p. 2025.01.23.634282). bioRxiv. https://doi.org/10.1101/2025.01.23.634282</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Girard-Buttoz, C., Neumann, C., Bortolato, T., Zaccarella, E., Friederici, A. D., Wittig, R. M., &amp; Crockford, C. (2025). Versatile use of chimpanzee call combinations promotes meaning expansion. Science Advances, 11(19), eadq2879. https://doi.org/10.1126/sciadv.adq2879; Crockford, C. (2019). Why does the chimpanzee vocal repertoire remain poorly understood and what can be done about it? In The Chimpanzees of the Taï Forest: 40 Years of Research, C. Boesch, R. M. Wittig, C. Crockford, L. Vigilant, T. Deschner, F. H. Leendertz, Eds. (pp. 394–409). Cambridge University Press.</t>
+  </si>
+  <si>
+    <t>Perodicticus potto</t>
+  </si>
+  <si>
+    <t>Piliocolobus badius</t>
+  </si>
+  <si>
+    <t>Pongo pygmaeus</t>
+  </si>
+  <si>
+    <t>Saguinus fuscicollis</t>
+  </si>
+  <si>
+    <t>Saguinus oedipus</t>
+  </si>
+  <si>
+    <t>Paulo-Morelo, M., &amp; Sánchez-Palomino, P. (2021). Descripción de las unidades fonéticas y sintaxis fonológica del repertorio vocal del tití cabeciblanco (Saguinus oedipus) silvestre. Biota colombiana, 22(1), 184–199. https://doi.org/10.21068/c2021.v22n01a12</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Semnopithecus entellus</t>
+  </si>
+  <si>
+    <t>Theropithecus gelada</t>
+  </si>
+  <si>
+    <t>Trachypithecus johnii</t>
+  </si>
+  <si>
+    <t>Varecia variegata</t>
+  </si>
+  <si>
+    <t>Batist, C. H., Razafindraibe, M. N., Randriamanantena, F., &amp; Baden, A. L. (2023). Bioacoustic characterization of the black-and-white ruffed lemur (Varecia variegata) vocal repertoire. Primates; Journal of Primatology, 64(6), 621–635. https://doi.org/10.1007/s10329-023-01083-8</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,1213 +552,864 @@
   <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>vocal_repertoire_size_MS2005</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>vocal_repertoire_size_MS2005_Source</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>vocal_repertoire_size_updated</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>vocal_repertoire_size_updated_Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Alouatta palliata</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Alouatta palliata</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
       <c r="C2">
         <v>22</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
       <c r="E2">
         <v>22</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Arctocebus calabarensis</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Arctocebus calabarensis</t>
-        </is>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D3" t="s">
+        <v>7</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Callicebus moloch</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Callicebus moloch</t>
-        </is>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Muir, J., Ravuri, A., Meissner, E., Hawes, J. E., Dufourq, E., O’Mahoney, T., &amp; Dunn, J. C. (2025). Detection and classification of captive coppery titi monkey calls. Bioacoustics, 34(4), 400–418. https://doi.org/10.1080/09524622.2025.2496497</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Callimico goeldii</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Callimico goeldii</t>
-        </is>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
       </c>
       <c r="C5">
         <v>28</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
       <c r="E5">
         <v>28</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
       </c>
       <c r="C6">
         <v>13</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D6" t="s">
+        <v>7</v>
       </c>
       <c r="E6">
         <v>8</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bosshard, A. B., Burkart, J. M., Merlo, P., Cathcart, C., Townsend, S. W., &amp; Bickel, B. (2024). Beyond bigrams: Call sequencing in the common marmoset (Callithrix jacchus) vocal system. Royal Society Open Science, 11(11), 240218. https://doi.org/10.1098/rsos.240218</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Callithrix pygmaea</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cebuella pygmaea</t>
-        </is>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
       </c>
       <c r="C7">
         <v>16</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D7" t="s">
+        <v>7</v>
       </c>
       <c r="E7">
         <v>16</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cebus olivaceus</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Cebus olivaceus</t>
-        </is>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
       </c>
       <c r="C8">
         <v>11</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
       <c r="E8">
         <v>11</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Cercocebus torquatus</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cercocebus torquatus</t>
-        </is>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
       </c>
       <c r="C9">
         <v>18</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Bouchet, H., Pellier, A.-S., Blois-Heulin, C., &amp; Lemasson, A. (2010). Sex differences in the vocal repertoire of adult red-capped mangabeys (Cercocebus torquatus): A multi-level acoustic analysis. American Journal of Primatology, 72(4), 360–375. https://doi.org/10.1002/ajp.20791</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cercopithecus cephus</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Cercopithecus cephus</t>
-        </is>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
       </c>
       <c r="C10">
         <v>16</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
       <c r="E10">
         <v>16</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chlorocebus aethiops</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Chlorocebus aethiops</t>
-        </is>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
       </c>
       <c r="C11">
         <v>25</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D11" t="s">
+        <v>7</v>
       </c>
       <c r="E11">
         <v>25</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Daubentonia madagascariensis</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Daubentonia madagascariensis</t>
-        </is>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
       </c>
       <c r="C12">
         <v>9</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D12" t="s">
+        <v>7</v>
       </c>
       <c r="E12">
         <v>9</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Eulemur fulvus</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Eulemur fulvus</t>
-        </is>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
       </c>
       <c r="C13">
         <v>20</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D13" t="s">
+        <v>7</v>
       </c>
       <c r="E13">
         <v>14</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Fichtel, C., &amp; Kappeler, P. M. (2022). Coevolution of social and communicative complexity in lemurs. Philosophical Transactions of the Royal Society B: Biological Sciences, 377(1860), 20210297. https://doi.org/10.1098/rstb.2021.0297
-Gamba, M., Friard, O., Riondato, I., Righini, R., Colombo, C., Miaretsoa, L., Torti, V., Nadhurou, B., &amp; Giacoma, C. (2015). Comparative Analysis of the Vocal Repertoire of Eulemur: A Dynamic Time Warping Approach. International Journal of Primatology, 36(5), 894–910. https://doi.org/10.1007/s10764-015-9861-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Eulemur macaco</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Eulemur macaco</t>
-        </is>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D14" t="s">
+        <v>7</v>
       </c>
       <c r="E14">
         <v>16</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Fichtel, C., &amp; Kappeler, P. M. (2022). Coevolution of social and communicative complexity in lemurs. Philosophical Transactions of the Royal Society B: Biological Sciences, 377(1860), 20210297. https://doi.org/10.1098/rstb.2021.0297</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Eulemur mongoz</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Eulemur mongoz</t>
-        </is>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
       </c>
       <c r="C15">
         <v>9</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
       <c r="E15">
         <v>15</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Nadhurou, B., Gamba, M., Andriaholinirina, N. V., Ouledi, A., &amp; Giacoma, C. (2016). The vocal communication of the mongoose lemur (Eulemur mongoz): Phonation mechanisms, acoustic features and quantitative analysis. Ethology Ecology &amp; Evolution, 28(3), 241–260. https://doi.org/10.1080/03949370.2015.1039069</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Euoticus elegantulus</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Euoticus elegantulus</t>
-        </is>
+      <c r="F15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
       </c>
       <c r="C16">
         <v>6</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D16" t="s">
+        <v>7</v>
       </c>
       <c r="E16">
         <v>6</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Galago alleni</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Galago alleni</t>
-        </is>
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
       </c>
       <c r="C17">
         <v>5</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D17" t="s">
+        <v>7</v>
       </c>
       <c r="E17">
         <v>5</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Galago senegalensis</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Galago senegalensis</t>
-        </is>
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
       </c>
       <c r="C18">
         <v>18</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D18" t="s">
+        <v>7</v>
       </c>
       <c r="E18">
         <v>18</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Galagoides demidoff</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Galago demidovii</t>
-        </is>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
       </c>
       <c r="C19">
         <v>8</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D19" t="s">
+        <v>7</v>
       </c>
       <c r="E19">
         <v>8</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
       </c>
       <c r="C20">
         <v>16</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D20" t="s">
+        <v>7</v>
       </c>
       <c r="E20">
         <v>17</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Salmi, R., Hammerschmidt, K., &amp; Doran-Sheehy, D. M. (2013). Western Gorilla Vocal Repertoire and Contextual Use of Vocalizations. Ethology, 119(10), 831–847. https://doi.org/10.1111/eth.12122</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Lagothrix lagothricha</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Lagothrix lagothricha</t>
-        </is>
+      <c r="F20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
       </c>
       <c r="C21">
         <v>6</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D21" t="s">
+        <v>7</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>León, J. J., Vargas, S. A., Ramírez, M. A., Galvis, N. F., Cifuentes, E. F., &amp; Stevenson, P. R. (2014). Vocal Communication in Woolly Monkeys (Lagothrixlagothricha lugens) in Cueva de los Guacharos National Park, Colombia. In T. R. Defler &amp; P. R. Stevenson (Eds), The Woolly Monkey: Behavior, Ecology, Systematics, and Captive Research (pp. 187–205). Springer. https://doi.org/10.1007/978-1-4939-0697-0 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
+      <c r="F21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
       </c>
       <c r="C22">
         <v>22</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D22" t="s">
+        <v>7</v>
       </c>
       <c r="E22">
         <v>22</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
       </c>
       <c r="C23">
         <v>16</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D23" t="s">
+        <v>7</v>
       </c>
       <c r="E23">
         <v>20</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Lopes, R. J. (2020). Mission marmoset. Nature, 579(7799), 464. https://doi.org/10.1038/d41586-020-00770-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
+      <c r="F23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
       </c>
       <c r="C24">
         <v>17</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D24" t="s">
+        <v>7</v>
       </c>
       <c r="E24">
         <v>17</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Macaca fuscata</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Macaca fuscata</t>
-        </is>
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
       </c>
       <c r="C25">
         <v>34</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D25" t="s">
+        <v>7</v>
       </c>
       <c r="E25">
         <v>34</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Macaca nemestrina</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Macaca nemestrina</t>
-        </is>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
       </c>
       <c r="C26">
         <v>16</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D26" t="s">
+        <v>7</v>
       </c>
       <c r="E26">
         <v>16</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Macaca radiata</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Macaca radiata</t>
-        </is>
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
       </c>
       <c r="C27">
         <v>21</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D27" t="s">
+        <v>7</v>
       </c>
       <c r="E27">
         <v>21</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Macaca silenus</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Macaca silenus</t>
-        </is>
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
       </c>
       <c r="C28">
         <v>15</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D28" t="s">
+        <v>7</v>
       </c>
       <c r="E28">
         <v>15</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
       </c>
       <c r="C29">
         <v>14</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D29" t="s">
+        <v>7</v>
       </c>
       <c r="E29">
         <v>14</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Mandrillus sphinx</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Mandrillus sphinx</t>
-        </is>
+      <c r="F29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
       </c>
       <c r="C30">
         <v>10</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D30" t="s">
+        <v>7</v>
       </c>
       <c r="E30">
         <v>10</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Miopithecus talapoin</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Miopithecus talapoin</t>
-        </is>
+      <c r="F30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
       </c>
       <c r="C31">
         <v>12</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D31" t="s">
+        <v>7</v>
       </c>
       <c r="E31">
         <v>12</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Pan paniscus</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Pan paniscus</t>
-        </is>
+      <c r="F31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
       </c>
       <c r="C32">
         <v>38</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D32" t="s">
+        <v>7</v>
       </c>
       <c r="E32">
         <v>11</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Wegdell, F., Schamberg, I., Berthet, M., Rothacher, Y., Dellwo, V., Surbeck, M., &amp; Townsend, S. W. (2025). An updated vocal repertoire of wild adult bonobos (Pan paniscus ) (p. 2025.01.23.634282). bioRxiv. https://doi.org/10.1101/2025.01.23.634282</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
+      <c r="F32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
       </c>
       <c r="C33">
         <v>29</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D33" t="s">
+        <v>7</v>
       </c>
       <c r="E33">
         <v>12</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Girard-Buttoz, C., Neumann, C., Bortolato, T., Zaccarella, E., Friederici, A. D., Wittig, R. M., &amp; Crockford, C. (2025). Versatile use of chimpanzee call combinations promotes meaning expansion. Science Advances, 11(19), eadq2879. https://doi.org/10.1126/sciadv.adq2879; Crockford, C. (2019). Why does the chimpanzee vocal repertoire remain poorly understood and what can be done about it? In The Chimpanzees of the Taï Forest: 40 Years of Research, C. Boesch, R. M. Wittig, C. Crockford, L. Vigilant, T. Deschner, F. H. Leendertz, Eds. (pp. 394–409). Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Perodicticus potto</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Perodicticus potto</t>
-        </is>
+      <c r="F33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
       </c>
       <c r="C34">
         <v>5</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D34" t="s">
+        <v>7</v>
       </c>
       <c r="E34">
         <v>5</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Piliocolobus badius</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Piliocolobus badius</t>
-        </is>
+      <c r="F34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
       </c>
       <c r="C35">
         <v>17</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D35" t="s">
+        <v>7</v>
       </c>
       <c r="E35">
         <v>17</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Pongo pygmaeus</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Pongo pygmaeus</t>
-        </is>
+      <c r="F35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" t="s">
+        <v>54</v>
       </c>
       <c r="C36">
         <v>10</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D36" t="s">
+        <v>7</v>
       </c>
       <c r="E36">
         <v>10</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Saguinus fuscicollis</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Saguinus fuscicollis</t>
-        </is>
+      <c r="F36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" t="s">
+        <v>55</v>
       </c>
       <c r="C37">
         <v>16</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D37" t="s">
+        <v>7</v>
       </c>
       <c r="E37">
         <v>16</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
+      <c r="F37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
       </c>
       <c r="C38">
         <v>33</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D38" t="s">
+        <v>7</v>
       </c>
       <c r="E38">
         <v>14</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Paulo-Morelo, M., &amp; Sánchez-Palomino, P. (2021). Descripción de las unidades fonéticas y sintaxis fonológica del repertorio vocal del tití cabeciblanco (Saguinus oedipus) silvestre. Biota colombiana, 22(1), 184–199. https://doi.org/10.21068/c2021.v22n01a12</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+      <c r="F38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" t="s">
+        <v>58</v>
       </c>
       <c r="C39">
         <v>21</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D39" t="s">
+        <v>7</v>
       </c>
       <c r="E39">
         <v>21</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Semnopithecus entellus</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Semnopithecus entellus</t>
-        </is>
+      <c r="F39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" t="s">
+        <v>59</v>
       </c>
       <c r="C40">
         <v>16</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D40" t="s">
+        <v>7</v>
       </c>
       <c r="E40">
         <v>16</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Theropithecus gelada</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Theropithecus gelada</t>
-        </is>
+      <c r="F40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" t="s">
+        <v>60</v>
       </c>
       <c r="C41">
         <v>22</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D41" t="s">
+        <v>7</v>
       </c>
       <c r="E41">
         <v>22</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Trachypithecus johnii</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Trachypithecus johnii</t>
-        </is>
+      <c r="F41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s">
+        <v>61</v>
       </c>
       <c r="C42">
         <v>16</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D42" t="s">
+        <v>7</v>
       </c>
       <c r="E42">
         <v>16</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Varecia variegata</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Varecia variegata</t>
-        </is>
+      <c r="F42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" t="s">
+        <v>62</v>
       </c>
       <c r="C43">
         <v>13</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>McComb, K., &amp; Semple, S. (2005). Coevolution of vocal communication and sociality in primates. Biology Letters, 1(4), 381-385.</t>
-        </is>
+      <c r="D43" t="s">
+        <v>7</v>
       </c>
       <c r="E43">
         <v>11</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Batist, C. H., Razafindraibe, M. N., Randriamanantena, F., &amp; Baden, A. L. (2023). Bioacoustic characterization of the black-and-white ruffed lemur (Varecia variegata) vocal repertoire. Primates; Journal of Primatology, 64(6), 621–635. https://doi.org/10.1007/s10329-023-01083-8</t>
-        </is>
+      <c r="F43" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1844,13 +1693,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0D7F67E-7D08-4BE0-A898-C0A5811FC1B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4650F383-8CC2-4DA2-B4CA-558A9541C447}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82ED1F59-D954-4FB9-8598-6CFE01C8DC04}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62939C94-D399-4338-94FA-009F101D8B65}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F885A6AD-2CE8-41E9-9298-F030E82C04FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB52B34-50DB-4F7A-8865-6B04A2E549E9}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1693,13 +1693,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4650F383-8CC2-4DA2-B4CA-558A9541C447}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282AC3AE-5B1C-4366-8621-E913DD8AE270}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62939C94-D399-4338-94FA-009F101D8B65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6B7CBA5-7DCF-4925-8DDF-EFDD6EF69295}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB52B34-50DB-4F7A-8865-6B04A2E549E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E4C155B-24A6-40B5-8A28-702A6D2DF0DE}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1693,13 +1693,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{282AC3AE-5B1C-4366-8621-E913DD8AE270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A5C77BB-979F-40E2-9D6E-72E30300AAD6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6B7CBA5-7DCF-4925-8DDF-EFDD6EF69295}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17E7F22C-42F3-4390-BA13-F0DF71893268}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E4C155B-24A6-40B5-8A28-702A6D2DF0DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8D738F-6F68-41D8-9765-28505BAC0AB4}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1415,291 +1415,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A5C77BB-979F-40E2-9D6E-72E30300AAD6}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17E7F22C-42F3-4390-BA13-F0DF71893268}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8D738F-6F68-41D8-9765-28505BAC0AB4}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1415,4 +1415,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A84E6FC-9F14-457B-8C4B-EB09A56AA5B8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C03E3D30-7D0A-440D-B462-0EEC36884403}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEA437F0-5E61-4741-8FF5-5366929EE212}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1415,291 +1415,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A84E6FC-9F14-457B-8C4B-EB09A56AA5B8}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C03E3D30-7D0A-440D-B462-0EEC36884403}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEA437F0-5E61-4741-8FF5-5366929EE212}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1415,4 +1415,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D3F905E-3FB6-434D-AA03-ED9A12880676}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5805F139-13BC-4DC6-97EC-11974E17BB3A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39595684-DEC9-45CF-AD32-865540A72EB0}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1693,13 +1693,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D3F905E-3FB6-434D-AA03-ED9A12880676}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D0F5B1F-A6CA-4DFE-90FF-EA1CF52C1607}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5805F139-13BC-4DC6-97EC-11974E17BB3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B571FC-C3BC-40D7-B645-1AE51F1935FC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39595684-DEC9-45CF-AD32-865540A72EB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D4101A4-5769-4E25-AC79-323FEBD1F8E7}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1693,13 +1693,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D0F5B1F-A6CA-4DFE-90FF-EA1CF52C1607}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FD790DB-D04A-4559-9EE0-6472304050BB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B571FC-C3BC-40D7-B645-1AE51F1935FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E92190C2-AC38-41FB-A568-97BF3E3A7E92}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D4101A4-5769-4E25-AC79-323FEBD1F8E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64E6510E-E1F9-4AF5-AF9E-70D6E69769C9}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1693,13 +1693,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FD790DB-D04A-4559-9EE0-6472304050BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1260D424-C7AB-4E50-BE54-F8DB6429D100}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E92190C2-AC38-41FB-A568-97BF3E3A7E92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{824A79F2-00AA-46CB-9E99-22A2879FE38A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64E6510E-E1F9-4AF5-AF9E-70D6E69769C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B68DD98-E9EE-4A98-8B51-6D4E6DB9CC11}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1415,291 +1415,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1260D424-C7AB-4E50-BE54-F8DB6429D100}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{824A79F2-00AA-46CB-9E99-22A2879FE38A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B68DD98-E9EE-4A98-8B51-6D4E6DB9CC11}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1415,4 +1415,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BEAE756-F9DB-4014-82D7-15CC431903E6}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6422B96F-3A0E-4CDC-B0A1-BFEAFAE7A5BA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7301F39-48E0-43BC-A052-8B0234C4205A}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="63">
   <si>
     <t>species_sci</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>Bosshard, A. B., Burkart, J. M., Merlo, P., Cathcart, C., Townsend, S. W., &amp; Bickel, B. (2024). Beyond bigrams: Call sequencing in the common marmoset (Callithrix jacchus) vocal system. Royal Society Open Science, 11(11), 240218. https://doi.org/10.1098/rsos.240218</t>
-  </si>
-  <si>
-    <t>Callithrix pygmaea</t>
   </si>
   <si>
     <t>Cebuella pygmaea</t>
@@ -677,7 +674,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>16</v>
@@ -694,10 +691,10 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>11</v>
@@ -714,10 +711,10 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>18</v>
@@ -729,15 +726,15 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>16</v>
@@ -754,10 +751,10 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>25</v>
@@ -774,10 +771,10 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -794,10 +791,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -809,15 +806,15 @@
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -829,15 +826,15 @@
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15">
         <v>9</v>
@@ -849,15 +846,15 @@
         <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -874,10 +871,10 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -894,10 +891,10 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18">
         <v>18</v>
@@ -914,10 +911,10 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
         <v>31</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -934,10 +931,10 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -949,15 +946,15 @@
         <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -969,15 +966,15 @@
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22">
         <v>22</v>
@@ -994,10 +991,10 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23">
         <v>16</v>
@@ -1009,15 +1006,15 @@
         <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>17</v>
@@ -1034,10 +1031,10 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25">
         <v>34</v>
@@ -1054,10 +1051,10 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26">
         <v>16</v>
@@ -1074,10 +1071,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C27">
         <v>21</v>
@@ -1094,10 +1091,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28">
         <v>15</v>
@@ -1114,10 +1111,10 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29">
         <v>14</v>
@@ -1134,10 +1131,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -1154,10 +1151,10 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31">
         <v>12</v>
@@ -1174,10 +1171,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32">
         <v>38</v>
@@ -1189,15 +1186,15 @@
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33">
         <v>29</v>
@@ -1209,15 +1206,15 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34">
         <v>5</v>
@@ -1234,10 +1231,10 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35">
         <v>17</v>
@@ -1254,10 +1251,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C36">
         <v>10</v>
@@ -1274,10 +1271,10 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37">
         <v>16</v>
@@ -1294,10 +1291,10 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38">
         <v>33</v>
@@ -1309,15 +1306,15 @@
         <v>14</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39">
         <v>21</v>
@@ -1334,10 +1331,10 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C40">
         <v>16</v>
@@ -1354,10 +1351,10 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C41">
         <v>22</v>
@@ -1374,10 +1371,10 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -1394,10 +1391,10 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43">
         <v>13</v>
@@ -1409,7 +1406,7 @@
         <v>11</v>
       </c>
       <c r="F43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1693,13 +1690,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BEAE756-F9DB-4014-82D7-15CC431903E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5C33CC-6BFF-4E1B-8058-8A1FBD8401B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6422B96F-3A0E-4CDC-B0A1-BFEAFAE7A5BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FE95121-2B4A-42C4-A160-2A064A4DBD79}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7301F39-48E0-43BC-A052-8B0234C4205A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0A090E1-9D60-4940-87C7-8FADC7373E2E}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1690,13 +1690,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5C33CC-6BFF-4E1B-8058-8A1FBD8401B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{567CBCF3-41AC-41F3-BF0D-E92D0B0862CA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FE95121-2B4A-42C4-A160-2A064A4DBD79}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCC4F323-F604-4410-B157-08A8A6D214BF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0A090E1-9D60-4940-87C7-8FADC7373E2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{937CD4AA-CC41-4F93-9572-111778E509C3}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1690,13 +1690,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{567CBCF3-41AC-41F3-BF0D-E92D0B0862CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89461835-002D-42BB-BB94-07D286C39BE6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCC4F323-F604-4410-B157-08A8A6D214BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABD67270-D14E-4921-BA76-AE73E365299B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{937CD4AA-CC41-4F93-9572-111778E509C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E720B49-6997-47CC-9055-45DFCF3B66F9}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1690,13 +1690,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89461835-002D-42BB-BB94-07D286C39BE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A092A24-3A17-4560-98BC-93BBC6186284}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABD67270-D14E-4921-BA76-AE73E365299B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4F10F78-439D-4183-BFB3-4E6E870FC80D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E720B49-6997-47CC-9055-45DFCF3B66F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DACDA9-7402-43DE-BBE2-87CD4ED4821A}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1690,13 +1690,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A092A24-3A17-4560-98BC-93BBC6186284}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61B34A34-7060-45EA-B012-7CD411CE7AEF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4F10F78-439D-4183-BFB3-4E6E870FC80D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{984B3290-974B-4F31-A665-B1BC77D19E9A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DACDA9-7402-43DE-BBE2-87CD4ED4821A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5437495-B511-4B55-B709-932F96741D11}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1412,291 +1412,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61B34A34-7060-45EA-B012-7CD411CE7AEF}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{984B3290-974B-4F31-A665-B1BC77D19E9A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5437495-B511-4B55-B709-932F96741D11}"/>
 </file>
--- a/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
+++ b/____EvoM1_TraitTable/vocal_repertoire_schniter.xlsx
@@ -1412,4 +1412,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01148D2E-C9ED-4054-8476-6F151432234B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A761EA4F-632C-456A-ACD0-9F31BA921F77}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B622F39-3E00-4D14-96F0-3784BB746AE7}"/>
 </file>